--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9942917B-7B85-4F36-AC8E-0CEF6C02FA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B61466-3F4A-428A-A27A-9A3D5519C11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
-  <si>
-    <t>Type</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -38,9 +35,6 @@
   </si>
   <si>
     <t>Extra</t>
-  </si>
-  <si>
-    <t>Shader</t>
   </si>
   <si>
     <t>COMPONENT_TYPE_SHADER_VTXTEX</t>
@@ -1043,10 +1037,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1062,110 +1056,89 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B61466-3F4A-428A-A27A-9A3D5519C11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC66090-07C1-4EB9-8BAF-E30E1AC3D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -86,6 +86,30 @@
   </si>
   <si>
     <t>VtxAnim</t>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_GHOST_EFFECT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_GhostAfterImage.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Static</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>VtxAnim</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_SMEAR_EFFECT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_SmearSkeletal.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1037,8 +1061,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="58.625" customWidth="1"/>
+    <col min="2" max="2" width="62.375" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1139,6 +1168,34 @@
       </c>
       <c r="E7" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC66090-07C1-4EB9-8BAF-E30E1AC3D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D90FB67-A133-4039-8961-5045BBE874EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -109,6 +109,29 @@
   </si>
   <si>
     <t>../../Client/Bin/Shaders/Shader_SmearSkeletal.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_PARTICLE_POINT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_VtxParticlePoint.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>VtxParticlePoint</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_EFFECT_MESH</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_VtxEffectMesh.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>VtxMesh</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1061,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.625" customWidth="1"/>
@@ -1198,6 +1221,34 @@
         <v>25</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D90FB67-A133-4039-8961-5045BBE874EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BF8F6B-D04E-4C72-B450-AEDFD0179706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>Id</t>
   </si>
@@ -132,6 +132,14 @@
   </si>
   <si>
     <t>VtxMesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_BILLBOARD</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_VtxEffectBillboard.hlsl</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1084,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.625" customWidth="1"/>
@@ -1249,6 +1257,20 @@
         <v>33</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BF8F6B-D04E-4C72-B450-AEDFD0179706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B94A0E-3C53-45CC-9E04-4A1FBBED1CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B94A0E-3C53-45CC-9E04-4A1FBBED1CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F663612-1453-4C69-8893-CD63280D93CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -140,6 +140,25 @@
   </si>
   <si>
     <t>../../Client/Bin/Shaders/Shader_VtxEffectBillboard.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_CHAKRA</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_ChakraMove.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>VtxTex</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_SWORD_TRAIL</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_Sword_Trail.hlsl</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1092,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.625" customWidth="1"/>
@@ -1271,6 +1290,34 @@
         <v>8</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F663612-1453-4C69-8893-CD63280D93CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688E2BCD-1133-4423-B6DE-17658D2351C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -159,6 +159,13 @@
   </si>
   <si>
     <t>../../Client/Bin/Shaders/Shader_Sword_Trail.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_SKYSPHERE</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_SkySphere.hlsl</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1111,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.625" customWidth="1"/>
@@ -1318,6 +1325,20 @@
         <v>38</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Shader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688E2BCD-1133-4423-B6DE-17658D2351C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FA3F91-E614-4AA4-ACED-FC39C1DD51ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E193459D-09E5-4EFC-999E-77506139C7EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -167,6 +167,13 @@
   <si>
     <t>../../Client/Bin/Shaders/Shader_SkySphere.hlsl</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Shaders/Shader_VtxEffectSkeletalMesh.hlsl</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPONENT_TYPE_SHADER_EFFECT_SKELETAL_MESH</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBF240-AF35-45A2-96AD-083D2B8612FA}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.625" customWidth="1"/>
@@ -1339,6 +1346,20 @@
         <v>33</v>
       </c>
     </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
